--- a/artfynd/A 19080-2024 artfynd.xlsx
+++ b/artfynd/A 19080-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118359399</v>
+        <v>118359400</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>90515</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -759,6 +759,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118359400</v>
+        <v>118359399</v>
       </c>
       <c r="B3" t="n">
-        <v>90515</v>
+        <v>78484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +790,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -861,7 +862,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 19080-2024 artfynd.xlsx
+++ b/artfynd/A 19080-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118359400</v>
+        <v>118359399</v>
       </c>
       <c r="B2" t="n">
-        <v>90515</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -759,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -778,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118359399</v>
+        <v>118359400</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>90522</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -862,6 +861,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
